--- a/data/ams_weekly_data/White_Mulberry/ads_report_week27.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week27.xlsx
@@ -4839,7 +4839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4902,19 +4902,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6649</v>
+        <v>4562</v>
       </c>
       <c r="E2" t="n">
-        <v>251</v>
+        <v>172</v>
       </c>
       <c r="F2" t="n">
-        <v>768.26</v>
+        <v>527.1185185000227</v>
       </c>
       <c r="G2" t="n">
-        <v>38733.455</v>
+        <v>26575.79649596139</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -4931,23 +4931,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6649</v>
+        <v>1702</v>
       </c>
       <c r="E3" t="n">
-        <v>251</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
-        <v>768.26</v>
+        <v>196.7064048069969</v>
       </c>
       <c r="G3" t="n">
-        <v>38733.455</v>
+        <v>9917.370003388956</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -4959,28 +4959,28 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6122</v>
+        <v>7034</v>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>266</v>
       </c>
       <c r="F4" t="n">
-        <v>924.27</v>
+        <v>812.6950766929804</v>
       </c>
       <c r="G4" t="n">
-        <v>1080.085</v>
+        <v>40973.74350064965</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -4997,20 +4997,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6122</v>
+        <v>4081</v>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="F5" t="n">
-        <v>924.27</v>
+        <v>616.1799999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>1080.085</v>
+        <v>720.0566666666667</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -5025,28 +5025,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SB-L shape-Multi Asin- KT- phrase</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12297</v>
+        <v>4081</v>
       </c>
       <c r="E6" t="n">
-        <v>187</v>
+        <v>75</v>
       </c>
       <c r="F6" t="n">
-        <v>1152.3225</v>
+        <v>616.1799999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>15054.4475</v>
+        <v>720.0566666666667</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -5058,28 +5058,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SB-L shape-Multi Asin- KT- phrase</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12297</v>
+        <v>4081</v>
       </c>
       <c r="E7" t="n">
-        <v>187</v>
+        <v>75</v>
       </c>
       <c r="F7" t="n">
-        <v>1152.3225</v>
+        <v>616.1799999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>15054.4475</v>
+        <v>720.0566666666667</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -5096,23 +5096,23 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12297</v>
+        <v>24152</v>
       </c>
       <c r="E8" t="n">
-        <v>187</v>
+        <v>368</v>
       </c>
       <c r="F8" t="n">
-        <v>1152.3225</v>
+        <v>2263.264513719916</v>
       </c>
       <c r="G8" t="n">
-        <v>15054.4475</v>
+        <v>29568.28214359218</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -5129,20 +5129,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12297</v>
+        <v>8505</v>
       </c>
       <c r="E9" t="n">
-        <v>187</v>
+        <v>130</v>
       </c>
       <c r="F9" t="n">
-        <v>1152.3225</v>
+        <v>796.9631037382362</v>
       </c>
       <c r="G9" t="n">
-        <v>15054.4475</v>
+        <v>10411.87619322224</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
@@ -5157,28 +5157,28 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1679</v>
+        <v>16531</v>
       </c>
       <c r="E10" t="n">
-        <v>34</v>
+        <v>252</v>
       </c>
       <c r="F10" t="n">
-        <v>340.24</v>
+        <v>1549.062382541848</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>20237.63166318558</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5199,19 +5199,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>251</v>
+        <v>1679</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="F11" t="n">
-        <v>33.89</v>
+        <v>340.24</v>
       </c>
       <c r="G11" t="n">
-        <v>2765.25</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -5223,28 +5223,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11551</v>
+        <v>251</v>
       </c>
       <c r="E12" t="n">
-        <v>115</v>
+        <v>7</v>
       </c>
       <c r="F12" t="n">
-        <v>1984.404414614359</v>
+        <v>33.89</v>
       </c>
       <c r="G12" t="n">
-        <v>8810.17</v>
+        <v>2765.25</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -5261,23 +5261,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1721</v>
+        <v>11551</v>
       </c>
       <c r="E13" t="n">
-        <v>17</v>
+        <v>115</v>
       </c>
       <c r="F13" t="n">
-        <v>295.6750572472966</v>
+        <v>1984.404414614359</v>
       </c>
       <c r="G13" t="n">
-        <v>1312.71</v>
+        <v>10073.65129215042</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -5294,23 +5294,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0FN4JG97R</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6477</v>
+        <v>1721</v>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="F14" t="n">
-        <v>1112.650528138344</v>
+        <v>295.6750572472966</v>
       </c>
       <c r="G14" t="n">
-        <v>4939.84</v>
+        <v>1500.967948146151</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -5322,28 +5322,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0FN4JG97R</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5044</v>
+        <v>6477</v>
       </c>
       <c r="E15" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="F15" t="n">
-        <v>393.83</v>
+        <v>1112.650528138344</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>5648.270759703427</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -5355,28 +5355,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4332</v>
+        <v>5044</v>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="F16" t="n">
-        <v>600.4362942379489</v>
+        <v>393.83</v>
       </c>
       <c r="G16" t="n">
-        <v>2160.170000000001</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -5393,23 +5393,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>7477</v>
+        <v>4332</v>
       </c>
       <c r="E17" t="n">
-        <v>92</v>
+        <v>53</v>
       </c>
       <c r="F17" t="n">
-        <v>1036.21867345174</v>
+        <v>600.4362942379489</v>
       </c>
       <c r="G17" t="n">
-        <v>3727.97</v>
+        <v>2160.170000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -5426,23 +5426,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2803</v>
+        <v>7477</v>
       </c>
       <c r="E18" t="n">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="F18" t="n">
-        <v>388.4350323103108</v>
+        <v>1036.21867345174</v>
       </c>
       <c r="G18" t="n">
-        <v>1397.46</v>
+        <v>3727.97</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -5454,25 +5454,25 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8914</v>
+        <v>2803</v>
       </c>
       <c r="E19" t="n">
-        <v>117</v>
+        <v>35</v>
       </c>
       <c r="F19" t="n">
-        <v>1832.48</v>
+        <v>388.4350323103108</v>
       </c>
       <c r="G19" t="n">
-        <v>2329.66</v>
+        <v>1397.46</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
@@ -5487,7 +5487,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>White Mulberry-Monitor Arm-Collective- SB - Phrase</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5496,19 +5496,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>541</v>
+        <v>8914</v>
       </c>
       <c r="E20" t="n">
-        <v>6</v>
+        <v>117</v>
       </c>
       <c r="F20" t="n">
-        <v>62.936</v>
+        <v>1832.48</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2329.66</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -5643,6 +5643,39 @@
         <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>White Mulberry-Monitor Arm-Collective- SB - Phrase</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>541</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="n">
+        <v>62.936</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week27.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week27.xlsx
@@ -2386,10 +2386,10 @@
         <v>7746</v>
       </c>
       <c r="G70" t="n">
-        <v>11773.73</v>
+        <v>13383.05</v>
       </c>
       <c r="H70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
@@ -4839,7 +4839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4902,19 +4902,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4562</v>
+        <v>6649</v>
       </c>
       <c r="E2" t="n">
-        <v>172</v>
+        <v>251</v>
       </c>
       <c r="F2" t="n">
-        <v>527.1185185000227</v>
+        <v>768.26</v>
       </c>
       <c r="G2" t="n">
-        <v>26575.79649596139</v>
+        <v>38733.455</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -4931,23 +4931,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1702</v>
+        <v>6649</v>
       </c>
       <c r="E3" t="n">
-        <v>64</v>
+        <v>251</v>
       </c>
       <c r="F3" t="n">
-        <v>196.7064048069969</v>
+        <v>768.26</v>
       </c>
       <c r="G3" t="n">
-        <v>9917.370003388956</v>
+        <v>38733.455</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -4959,28 +4959,28 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7034</v>
+        <v>6122</v>
       </c>
       <c r="E4" t="n">
-        <v>266</v>
+        <v>112</v>
       </c>
       <c r="F4" t="n">
-        <v>812.6950766929804</v>
+        <v>924.27</v>
       </c>
       <c r="G4" t="n">
-        <v>40973.74350064965</v>
+        <v>1080.085</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -4997,20 +4997,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4081</v>
+        <v>6122</v>
       </c>
       <c r="E5" t="n">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="F5" t="n">
-        <v>616.1799999999999</v>
+        <v>924.27</v>
       </c>
       <c r="G5" t="n">
-        <v>720.0566666666667</v>
+        <v>1080.085</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -5025,28 +5025,28 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4081</v>
+        <v>12297</v>
       </c>
       <c r="E6" t="n">
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="F6" t="n">
-        <v>616.1799999999999</v>
+        <v>1152.3225</v>
       </c>
       <c r="G6" t="n">
-        <v>720.0566666666667</v>
+        <v>15054.4475</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -5058,28 +5058,28 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4081</v>
+        <v>12297</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="F7" t="n">
-        <v>616.1799999999999</v>
+        <v>1152.3225</v>
       </c>
       <c r="G7" t="n">
-        <v>720.0566666666667</v>
+        <v>15054.4475</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -5096,23 +5096,23 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24152</v>
+        <v>12297</v>
       </c>
       <c r="E8" t="n">
-        <v>368</v>
+        <v>187</v>
       </c>
       <c r="F8" t="n">
-        <v>2263.264513719916</v>
+        <v>1152.3225</v>
       </c>
       <c r="G8" t="n">
-        <v>29568.28214359218</v>
+        <v>15054.4475</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -5129,20 +5129,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8505</v>
+        <v>12297</v>
       </c>
       <c r="E9" t="n">
-        <v>130</v>
+        <v>187</v>
       </c>
       <c r="F9" t="n">
-        <v>796.9631037382362</v>
+        <v>1152.3225</v>
       </c>
       <c r="G9" t="n">
-        <v>10411.87619322224</v>
+        <v>15054.4475</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
@@ -5157,28 +5157,28 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SB-L shape-Multi Asin- KT- phrase</t>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0DP2WC5VW</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16531</v>
+        <v>1679</v>
       </c>
       <c r="E10" t="n">
-        <v>252</v>
+        <v>34</v>
       </c>
       <c r="F10" t="n">
-        <v>1549.062382541848</v>
+        <v>340.24</v>
       </c>
       <c r="G10" t="n">
-        <v>20237.63166318558</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+          <t>WM-SB-Monitor Arms-Branded</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5199,19 +5199,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1679</v>
+        <v>251</v>
       </c>
       <c r="E11" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>340.24</v>
+        <v>33.89</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2765.25</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -5223,28 +5223,28 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WM-SB-Monitor Arms-Branded</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B0DP2WC5VW</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>251</v>
+        <v>11551</v>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="F12" t="n">
-        <v>33.89</v>
+        <v>1984.404414614359</v>
       </c>
       <c r="G12" t="n">
-        <v>2765.25</v>
+        <v>11808.02892741152</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -5261,23 +5261,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11551</v>
+        <v>1721</v>
       </c>
       <c r="E13" t="n">
-        <v>115</v>
+        <v>17</v>
       </c>
       <c r="F13" t="n">
-        <v>1984.404414614359</v>
+        <v>295.6750572472966</v>
       </c>
       <c r="G13" t="n">
-        <v>10073.65129215042</v>
+        <v>1759.389166531676</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -5294,23 +5294,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0FN4JG97R</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1721</v>
+        <v>6477</v>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="F14" t="n">
-        <v>295.6750572472966</v>
+        <v>1112.650528138344</v>
       </c>
       <c r="G14" t="n">
-        <v>1500.967948146151</v>
+        <v>6620.731906056808</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -5322,28 +5322,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0FN4JG97R</t>
+          <t>B0DP2Z5DQ9</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6477</v>
+        <v>5044</v>
       </c>
       <c r="E15" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="F15" t="n">
-        <v>1112.650528138344</v>
+        <v>393.83</v>
       </c>
       <c r="G15" t="n">
-        <v>5648.270759703427</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -5355,28 +5355,28 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0DP2Z5DQ9</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5044</v>
+        <v>4332</v>
       </c>
       <c r="E16" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="F16" t="n">
-        <v>393.83</v>
+        <v>600.4362942379489</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2160.170000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -5393,23 +5393,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4332</v>
+        <v>7477</v>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="F17" t="n">
-        <v>600.4362942379489</v>
+        <v>1036.21867345174</v>
       </c>
       <c r="G17" t="n">
-        <v>2160.170000000001</v>
+        <v>3727.97</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -5426,23 +5426,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7477</v>
+        <v>2803</v>
       </c>
       <c r="E18" t="n">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="F18" t="n">
-        <v>1036.21867345174</v>
+        <v>388.4350323103108</v>
       </c>
       <c r="G18" t="n">
-        <v>3727.97</v>
+        <v>1397.46</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -5454,25 +5454,25 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2803</v>
+        <v>8914</v>
       </c>
       <c r="E19" t="n">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="F19" t="n">
-        <v>388.4350323103108</v>
+        <v>1832.48</v>
       </c>
       <c r="G19" t="n">
-        <v>1397.46</v>
+        <v>2329.66</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
@@ -5487,7 +5487,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
+          <t>White Mulberry-Monitor Arm-Collective- SB - Phrase</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5496,19 +5496,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8914</v>
+        <v>541</v>
       </c>
       <c r="E20" t="n">
-        <v>117</v>
+        <v>6</v>
       </c>
       <c r="F20" t="n">
-        <v>1832.48</v>
+        <v>62.936</v>
       </c>
       <c r="G20" t="n">
-        <v>2329.66</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0DB5VG39T</t>
+          <t>B0DB5VVPSB</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0DB5VVPSB</t>
+          <t>B0DB5W4TCP</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0DB5W4TCP</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -5643,39 +5643,6 @@
         <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>White Mulberry-Monitor Arm-Collective- SB - Phrase</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>B0DP32F346</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>541</v>
-      </c>
-      <c r="E25" t="n">
-        <v>6</v>
-      </c>
-      <c r="F25" t="n">
-        <v>62.936</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>
